--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>72.343</v>
+        <v>67.96940000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>71.07340000000001</v>
+        <v>62.5825</v>
       </c>
       <c r="F2" t="n">
-        <v>1.269599999999999</v>
+        <v>5.387</v>
       </c>
       <c r="G2" t="n">
-        <v>53.8161</v>
+        <v>61.9302</v>
       </c>
       <c r="H2" t="n">
-        <v>53.4178</v>
+        <v>22.0176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3987999999999991</v>
+        <v>39.9122</v>
       </c>
       <c r="J2" t="n">
-        <v>82.0211</v>
+        <v>94.25830000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>69.92659999999999</v>
+        <v>40.7201</v>
       </c>
       <c r="L2" t="n">
-        <v>12.0946</v>
+        <v>53.5383</v>
       </c>
       <c r="M2" t="n">
-        <v>-28.2051</v>
+        <v>-32.328</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.5092</v>
+        <v>-18.7026</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.6958</v>
+        <v>-13.6257</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0001999999999997559</v>
+        <v>-19.0153</v>
       </c>
       <c r="Q2" t="n">
-        <v>-43.6573</v>
+        <v>-63.0605</v>
       </c>
       <c r="R2" t="n">
-        <v>43.6576</v>
+        <v>44.0455</v>
       </c>
       <c r="S2" t="n">
-        <v>17.4121</v>
+        <v>7.8277</v>
       </c>
       <c r="T2" t="n">
-        <v>13.9963</v>
+        <v>4.0432</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4157</v>
+        <v>3.7841</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1146</v>
+        <v>17.2268</v>
       </c>
       <c r="W2" t="n">
-        <v>18.713</v>
+        <v>27.3416</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.5983</v>
+        <v>-10.1146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>54.136</v>
+        <v>65.4205</v>
       </c>
       <c r="E3" t="n">
-        <v>49.7646</v>
+        <v>65.2936</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3712</v>
+        <v>0.1267</v>
       </c>
       <c r="G3" t="n">
-        <v>61.9302</v>
+        <v>53.8161</v>
       </c>
       <c r="H3" t="n">
-        <v>22.0176</v>
+        <v>53.4178</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9122</v>
+        <v>0.3987999999999991</v>
       </c>
       <c r="J3" t="n">
-        <v>94.25830000000001</v>
+        <v>82.0211</v>
       </c>
       <c r="K3" t="n">
-        <v>40.7201</v>
+        <v>69.92659999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>53.5383</v>
+        <v>12.0946</v>
       </c>
       <c r="M3" t="n">
-        <v>-32.328</v>
+        <v>-28.2051</v>
       </c>
       <c r="N3" t="n">
-        <v>-18.7026</v>
+        <v>-16.5092</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.6257</v>
+        <v>-11.6958</v>
       </c>
       <c r="P3" t="n">
-        <v>-19.0153</v>
+        <v>-0.0001999999999997559</v>
       </c>
       <c r="Q3" t="n">
-        <v>-63.0605</v>
+        <v>-43.6573</v>
       </c>
       <c r="R3" t="n">
-        <v>44.0455</v>
+        <v>43.6576</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.0063</v>
+        <v>10.4899</v>
       </c>
       <c r="T3" t="n">
-        <v>-8.7746</v>
+        <v>8.216900000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7684</v>
+        <v>2.273</v>
       </c>
       <c r="V3" t="n">
-        <v>17.2268</v>
+        <v>1.1146</v>
       </c>
       <c r="W3" t="n">
-        <v>27.3416</v>
+        <v>18.713</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.1146</v>
+        <v>-17.5983</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>46.9833</v>
+        <v>56.4148</v>
       </c>
       <c r="E4" t="n">
-        <v>55.6368</v>
+        <v>61.3872</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.6534</v>
+        <v>-4.9721</v>
       </c>
       <c r="G4" t="n">
         <v>52.058</v>
@@ -766,13 +766,13 @@
         <v>47.1499</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.7751</v>
+        <v>3.6568</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.1259</v>
+        <v>3.6245</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6489</v>
+        <v>0.03209999999999991</v>
       </c>
       <c r="V4" t="n">
         <v>-3.7626</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>31.5898</v>
+        <v>46.1964</v>
       </c>
       <c r="E5" t="n">
-        <v>39.8342</v>
+        <v>45.611</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.2445</v>
+        <v>0.5857999999999997</v>
       </c>
       <c r="G5" t="n">
-        <v>29.4452</v>
+        <v>13.5191</v>
       </c>
       <c r="H5" t="n">
-        <v>22.2041</v>
+        <v>0.6194999999999993</v>
       </c>
       <c r="I5" t="n">
-        <v>7.241099999999999</v>
+        <v>12.9001</v>
       </c>
       <c r="J5" t="n">
-        <v>46.1491</v>
+        <v>38.3723</v>
       </c>
       <c r="K5" t="n">
-        <v>32.0118</v>
+        <v>17.4417</v>
       </c>
       <c r="L5" t="n">
-        <v>14.1375</v>
+        <v>20.9309</v>
       </c>
       <c r="M5" t="n">
-        <v>-16.7039</v>
+        <v>-24.8532</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.8078</v>
+        <v>-16.8223</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.8962</v>
+        <v>-8.030900000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9403</v>
+        <v>10.2838</v>
       </c>
       <c r="Q5" t="n">
-        <v>-22.5079</v>
+        <v>-28.3288</v>
       </c>
       <c r="R5" t="n">
-        <v>20.5674</v>
+        <v>38.6125</v>
       </c>
       <c r="S5" t="n">
-        <v>11.1255</v>
+        <v>-3.2735</v>
       </c>
       <c r="T5" t="n">
-        <v>9.275</v>
+        <v>-1.5181</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8501</v>
+        <v>-1.7556</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.040299999999999</v>
+        <v>25.6674</v>
       </c>
       <c r="W5" t="n">
-        <v>6.9179</v>
+        <v>37.0847</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.9583</v>
+        <v>-11.4175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>30.879</v>
+        <v>26.719</v>
       </c>
       <c r="E6" t="n">
-        <v>36.5337</v>
+        <v>26.7549</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.6547</v>
+        <v>-0.03540000000000032</v>
       </c>
       <c r="G6" t="n">
-        <v>13.5191</v>
+        <v>29.5329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6194999999999993</v>
+        <v>16.3241</v>
       </c>
       <c r="I6" t="n">
-        <v>12.9001</v>
+        <v>13.2091</v>
       </c>
       <c r="J6" t="n">
-        <v>38.3723</v>
+        <v>40.6414</v>
       </c>
       <c r="K6" t="n">
-        <v>17.4417</v>
+        <v>23.9006</v>
       </c>
       <c r="L6" t="n">
-        <v>20.9309</v>
+        <v>16.7407</v>
       </c>
       <c r="M6" t="n">
-        <v>-24.8532</v>
+        <v>-11.1083</v>
       </c>
       <c r="N6" t="n">
-        <v>-16.8223</v>
+        <v>-7.5766</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.030900000000001</v>
+        <v>-3.5317</v>
       </c>
       <c r="P6" t="n">
-        <v>10.2838</v>
+        <v>2.1344</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.3288</v>
+        <v>-22.1199</v>
       </c>
       <c r="R6" t="n">
-        <v>38.6125</v>
+        <v>24.2541</v>
       </c>
       <c r="S6" t="n">
-        <v>-18.591</v>
+        <v>2.4035</v>
       </c>
       <c r="T6" t="n">
-        <v>-10.5953</v>
+        <v>2.587</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.9964</v>
+        <v>-0.1830999999999998</v>
       </c>
       <c r="V6" t="n">
-        <v>25.6674</v>
+        <v>-7.351800000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>37.0847</v>
+        <v>5.6462</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.4175</v>
+        <v>-12.998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>28.6725</v>
+        <v>25.965</v>
       </c>
       <c r="E7" t="n">
-        <v>28.6753</v>
+        <v>35.011</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.002700000000000813</v>
+        <v>-9.046000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>29.5329</v>
+        <v>29.4452</v>
       </c>
       <c r="H7" t="n">
-        <v>16.3241</v>
+        <v>22.2041</v>
       </c>
       <c r="I7" t="n">
-        <v>13.2091</v>
+        <v>7.241099999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>40.6414</v>
+        <v>46.1491</v>
       </c>
       <c r="K7" t="n">
-        <v>23.9006</v>
+        <v>32.0118</v>
       </c>
       <c r="L7" t="n">
-        <v>16.7407</v>
+        <v>14.1375</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.1083</v>
+        <v>-16.7039</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.5766</v>
+        <v>-9.8078</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.5317</v>
+        <v>-6.8962</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q7" t="n">
-        <v>-22.1199</v>
+        <v>-22.5079</v>
       </c>
       <c r="R7" t="n">
-        <v>24.2541</v>
+        <v>20.5674</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3573</v>
+        <v>5.5001</v>
       </c>
       <c r="T7" t="n">
-        <v>4.507300000000001</v>
+        <v>4.4517</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1499999999999998</v>
+        <v>1.0485</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.351800000000001</v>
+        <v>-7.040299999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>5.6462</v>
+        <v>6.9179</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.998</v>
+        <v>-13.9583</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>7.143</v>
+        <v>5.2988</v>
       </c>
       <c r="E8" t="n">
-        <v>8.570600000000001</v>
+        <v>6.3289</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4278</v>
+        <v>-1.0302</v>
       </c>
       <c r="G8" t="n">
         <v>2.419</v>
@@ -1078,13 +1078,13 @@
         <v>5.821</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7283</v>
+        <v>-0.1157</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4428</v>
+        <v>0.201</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7144000000000001</v>
+        <v>-0.3167</v>
       </c>
       <c r="V8" t="n">
         <v>0.08499999999999994</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>5.4056</v>
+        <v>5.0084</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2103</v>
+        <v>-0.4362000000000004</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8045</v>
+        <v>5.444599999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.600600000000001</v>
+        <v>6.8183</v>
       </c>
       <c r="H9" t="n">
-        <v>18.85</v>
+        <v>2.1841</v>
       </c>
       <c r="I9" t="n">
-        <v>-22.4506</v>
+        <v>4.6341</v>
       </c>
       <c r="J9" t="n">
-        <v>25.4744</v>
+        <v>12.9705</v>
       </c>
       <c r="K9" t="n">
-        <v>32.8647</v>
+        <v>3.6872</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.3905</v>
+        <v>9.2837</v>
       </c>
       <c r="M9" t="n">
-        <v>-29.0746</v>
+        <v>-6.152399999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.0145</v>
+        <v>-1.5029</v>
       </c>
       <c r="O9" t="n">
-        <v>-15.0604</v>
+        <v>-4.6492</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1046</v>
+        <v>-3.4925</v>
       </c>
       <c r="Q9" t="n">
-        <v>-40.9411</v>
+        <v>-17.269</v>
       </c>
       <c r="R9" t="n">
-        <v>44.0453</v>
+        <v>13.7763</v>
       </c>
       <c r="S9" t="n">
-        <v>21.262</v>
+        <v>0.2246000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>13.2349</v>
+        <v>0.05159999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>8.0274</v>
+        <v>0.1732</v>
       </c>
       <c r="V9" t="n">
-        <v>-15.3605</v>
+        <v>1.4583</v>
       </c>
       <c r="W9" t="n">
-        <v>10.4414</v>
+        <v>3.8105</v>
       </c>
       <c r="X9" t="n">
-        <v>-25.8024</v>
+        <v>-2.3523</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>G. MATÍAS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6895</v>
+        <v>1.7672</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5244</v>
+        <v>1.3792</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.8352</v>
+        <v>0.388</v>
       </c>
       <c r="G10" t="n">
-        <v>-17.0595</v>
+        <v>1.2791</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.5178</v>
+        <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.541499999999999</v>
+        <v>1.2585</v>
       </c>
       <c r="J10" t="n">
-        <v>12.6303</v>
+        <v>1.2791</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4258</v>
+        <v>0.0206</v>
       </c>
       <c r="L10" t="n">
-        <v>11.2047</v>
+        <v>1.2585</v>
       </c>
       <c r="M10" t="n">
-        <v>-29.6896</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-11.9434</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-17.7462</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>19.0151</v>
+        <v>0.388</v>
       </c>
       <c r="Q10" t="n">
-        <v>-25.4184</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>44.4334</v>
+        <v>0.388</v>
       </c>
       <c r="S10" t="n">
-        <v>30.7497</v>
+        <v>0.1001</v>
       </c>
       <c r="T10" t="n">
-        <v>25.1975</v>
+        <v>0.1001</v>
       </c>
       <c r="U10" t="n">
-        <v>5.5524</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-31.0162</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1149</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-32.1311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MATÍAS RODRÍGUEZ</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6671</v>
+        <v>-0.04809999999999987</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2791</v>
+        <v>0.6894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.388</v>
+        <v>-0.7378</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2791</v>
+        <v>-4.448700000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0206</v>
+        <v>-12.4329</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2585</v>
+        <v>7.984299999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2791</v>
+        <v>10.598</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0206</v>
+        <v>2.3854</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2585</v>
+        <v>8.2126</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-15.0469</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-14.8184</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.2282000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.388</v>
+        <v>-1.7465</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-27.3587</v>
       </c>
       <c r="R11" t="n">
-        <v>0.388</v>
+        <v>25.6123</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-2.8202</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1.6062</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1.2138</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.966999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>19.0565</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-10.0894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>V. ESPAÑOL BERENGUER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.021199999999999</v>
+        <v>-1.2005</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.581399999999999</v>
+        <v>0.256</v>
       </c>
       <c r="F12" t="n">
-        <v>4.6027</v>
+        <v>-1.4565</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8183</v>
+        <v>-0.8249</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1841</v>
+        <v>-0.4539</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6341</v>
+        <v>-0.3709</v>
       </c>
       <c r="J12" t="n">
-        <v>12.9705</v>
+        <v>0.1436</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6872</v>
+        <v>0.103</v>
       </c>
       <c r="L12" t="n">
-        <v>9.2837</v>
+        <v>0.0406</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.152399999999999</v>
+        <v>-0.9685</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5029</v>
+        <v>-0.5569</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.6492</v>
+        <v>-0.4115</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4925</v>
+        <v>0.3881</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.269</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>13.7763</v>
+        <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7627</v>
+        <v>-0.1517</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0936</v>
+        <v>0.1124</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6690999999999999</v>
+        <v>-0.2642</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4583</v>
+        <v>-0.6119</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8105</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3523</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. ESPAÑOL BERENGUER</t>
+          <t>M. BENÍTEZ MONTESINOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3823</v>
+        <v>-1.9534</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1559</v>
+        <v>-0.9296</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5382</v>
+        <v>-1.0239</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8249</v>
+        <v>-0.9833</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4539</v>
+        <v>-0.6179</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3709</v>
+        <v>-0.3654</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1436</v>
+        <v>0.0406</v>
       </c>
       <c r="K13" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0.0406</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9685</v>
+        <v>-1.0239</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5569</v>
+        <v>-0.6179</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4115</v>
+        <v>-0.406</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3881</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q13" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.3881</v>
-      </c>
       <c r="S13" t="n">
-        <v>-0.3335</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01230000000000001</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3459</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. BENÍTEZ MONTESINOS</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9534</v>
+        <v>-2.8349</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9296</v>
+        <v>1.992999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0239</v>
+        <v>-4.827999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9833</v>
+        <v>-3.600600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6179</v>
+        <v>18.85</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3654</v>
+        <v>-22.4506</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0406</v>
+        <v>25.4744</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>32.8647</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0406</v>
+        <v>-7.3905</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0239</v>
+        <v>-29.0746</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6179</v>
+        <v>-14.0145</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.406</v>
+        <v>-15.0604</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9702</v>
+        <v>3.1046</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>-40.9411</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>44.0453</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>13.0219</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>7.017799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6.0038</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-15.3605</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>10.4414</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-25.8024</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.8899</v>
+        <v>-2.9922</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9916</v>
+        <v>-1.2303</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8983</v>
+        <v>-1.762</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4914</v>
@@ -1624,13 +1624,13 @@
         <v>0.9701</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9522</v>
+        <v>-0.05479999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1089</v>
+        <v>0.6524</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8435</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2821</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.680700000000001</v>
+        <v>-9.1922</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.398800000000001</v>
+        <v>-0.1309999999999993</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2821</v>
+        <v>-9.061299999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.448700000000001</v>
+        <v>-11.6795</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.4329</v>
+        <v>-16.3696</v>
       </c>
       <c r="I16" t="n">
-        <v>7.984299999999999</v>
+        <v>4.689799999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>10.598</v>
+        <v>14.5493</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3854</v>
+        <v>-3.1097</v>
       </c>
       <c r="L16" t="n">
-        <v>8.2126</v>
+        <v>17.659</v>
       </c>
       <c r="M16" t="n">
-        <v>-15.0469</v>
+        <v>-26.2288</v>
       </c>
       <c r="N16" t="n">
-        <v>-14.8184</v>
+        <v>-13.2597</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2282000000000001</v>
+        <v>-12.969</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7465</v>
+        <v>7.567200000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-27.3587</v>
+        <v>-20.9557</v>
       </c>
       <c r="R16" t="n">
-        <v>25.6123</v>
+        <v>28.5227</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.4526</v>
+        <v>-0.2174999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.6945</v>
+        <v>0.2037</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7582</v>
+        <v>-0.4211000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>8.966999999999999</v>
+        <v>-4.8624</v>
       </c>
       <c r="W16" t="n">
-        <v>19.0565</v>
+        <v>6.0715</v>
       </c>
       <c r="X16" t="n">
-        <v>-10.0894</v>
+        <v>-10.9341</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.5282</v>
+        <v>-12.4741</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3144</v>
+        <v>0.4979000000000005</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.2135</v>
+        <v>-12.9722</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.6795</v>
+        <v>-17.0595</v>
       </c>
       <c r="H17" t="n">
-        <v>-16.3696</v>
+        <v>-10.5178</v>
       </c>
       <c r="I17" t="n">
-        <v>4.689799999999999</v>
+        <v>-6.541499999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>14.5493</v>
+        <v>12.6303</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.1097</v>
+        <v>1.4258</v>
       </c>
       <c r="L17" t="n">
-        <v>17.659</v>
+        <v>11.2047</v>
       </c>
       <c r="M17" t="n">
-        <v>-26.2288</v>
+        <v>-29.6896</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.2597</v>
+        <v>-11.9434</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.969</v>
+        <v>-17.7462</v>
       </c>
       <c r="P17" t="n">
-        <v>7.567200000000001</v>
+        <v>19.0151</v>
       </c>
       <c r="Q17" t="n">
-        <v>-20.9557</v>
+        <v>-25.4184</v>
       </c>
       <c r="R17" t="n">
-        <v>28.5227</v>
+        <v>44.4334</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.5534</v>
+        <v>16.5863</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.98</v>
+        <v>12.1711</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5736</v>
+        <v>4.4151</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.8624</v>
+        <v>-31.0162</v>
       </c>
       <c r="W17" t="n">
-        <v>6.0715</v>
+        <v>1.1149</v>
       </c>
       <c r="X17" t="n">
-        <v>-10.9341</v>
+        <v>-32.1311</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.7642</v>
+        <v>-14.3625</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4011</v>
+        <v>6.7454</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.1656</v>
+        <v>-21.1082</v>
       </c>
       <c r="G18" t="n">
         <v>-8.3393</v>
@@ -1858,13 +1858,13 @@
         <v>28.135</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.444800000000001</v>
+        <v>-3.043</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.2435</v>
+        <v>0.1008999999999998</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.2009</v>
+        <v>-3.1439</v>
       </c>
       <c r="V18" t="n">
         <v>-18.8911</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>237.3313</v>
+        <v>255.7016</v>
       </c>
       <c r="E19" t="n">
-        <v>305.4436</v>
+        <v>311.8029</v>
       </c>
       <c r="F19" t="n">
-        <v>-68.1129</v>
+        <v>-56.10150000000002</v>
       </c>
       <c r="G19" t="n">
         <v>202.3907</v>
@@ -1936,16 +1936,16 @@
         <v>410.3792</v>
       </c>
       <c r="S19" t="n">
-        <v>31.76329999999999</v>
+        <v>50.1345</v>
       </c>
       <c r="T19" t="n">
-        <v>34.0498</v>
+        <v>40.41</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.286899999999999</v>
+        <v>9.724200000000002</v>
       </c>
       <c r="V19" t="n">
-        <v>-34.6598</v>
+        <v>-34.65980000000001</v>
       </c>
       <c r="W19" t="n">
         <v>166.5515</v>
